--- a/data/trans_bre/P2A_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2A_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-31,49; -0,95</t>
+          <t>-30,99; 0,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,32; 18,61</t>
+          <t>-10,85; 18,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 25,06</t>
+          <t>-8,86; 24,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-25,98; 11,45</t>
+          <t>-26,48; 10,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-45,46; -1,72</t>
+          <t>-44,64; 1,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-24,01; 55,34</t>
+          <t>-22,24; 49,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-15,72; 84,7</t>
+          <t>-19,87; 84,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-37,6; 17,74</t>
+          <t>-38,12; 17,17</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 2,58</t>
+          <t>-9,1; 2,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 5,07</t>
+          <t>-7,54; 4,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 4,33</t>
+          <t>-7,25; 4,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 12,78</t>
+          <t>-1,78; 10,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-24,11; 7,91</t>
+          <t>-24,0; 8,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-20,15; 15,48</t>
+          <t>-19,71; 15,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-18,75; 13,39</t>
+          <t>-20,0; 13,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 18,38</t>
+          <t>-2,25; 14,57</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 6,07</t>
+          <t>-12,25; 6,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 13,05</t>
+          <t>-6,58; 12,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 13,16</t>
+          <t>-5,35; 13,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 8,16</t>
+          <t>-8,48; 7,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-33,5; 25,66</t>
+          <t>-32,8; 23,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,51; 50,65</t>
+          <t>-18,65; 47,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-13,68; 48,61</t>
+          <t>-15,45; 50,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 10,83</t>
+          <t>-10,42; 10,67</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 0,33</t>
+          <t>-9,33; -0,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 5,1</t>
+          <t>-4,85; 4,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 5,22</t>
+          <t>-4,17; 5,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 7,46</t>
+          <t>-2,43; 8,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,54; 1,02</t>
+          <t>-23,34; -0,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,67; 15,46</t>
+          <t>-12,81; 14,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-11,5; 16,36</t>
+          <t>-11,57; 17,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 10,23</t>
+          <t>-3,11; 11,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2A_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-30,99; 0,69</t>
+          <t>-31,86; -0,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,85; 18,06</t>
+          <t>-11,27; 18,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 24,84</t>
+          <t>-7,34; 26,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-26,48; 10,95</t>
+          <t>-26,83; 13,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-44,64; 1,63</t>
+          <t>-45,74; -0,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-22,24; 49,87</t>
+          <t>-22,33; 52,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-19,87; 84,42</t>
+          <t>-17,27; 91,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-38,12; 17,17</t>
+          <t>-36,63; 21,78</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 2,78</t>
+          <t>-8,47; 3,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 4,78</t>
+          <t>-7,81; 4,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 4,09</t>
+          <t>-7,19; 4,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 10,6</t>
+          <t>-1,74; 11,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-24,0; 8,89</t>
+          <t>-21,82; 10,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,71; 15,19</t>
+          <t>-20,34; 12,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,0; 13,71</t>
+          <t>-19,97; 14,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 14,57</t>
+          <t>-2,16; 16,82</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 6,4</t>
+          <t>-13,24; 5,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 12,51</t>
+          <t>-5,63; 12,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 13,16</t>
+          <t>-5,19; 13,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 7,9</t>
+          <t>-8,25; 7,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-32,8; 23,48</t>
+          <t>-35,3; 20,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,65; 47,46</t>
+          <t>-16,2; 50,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-15,45; 50,43</t>
+          <t>-16,51; 51,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,42; 10,67</t>
+          <t>-10,25; 10,35</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,33; -0,18</t>
+          <t>-8,94; 0,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 4,83</t>
+          <t>-4,79; 5,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 5,38</t>
+          <t>-3,83; 5,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 8,01</t>
+          <t>-2,8; 7,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,34; -0,03</t>
+          <t>-22,7; 1,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,81; 14,58</t>
+          <t>-12,64; 16,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-11,57; 17,29</t>
+          <t>-10,79; 18,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 11,05</t>
+          <t>-3,54; 10,91</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2A_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-5,62</t>
+          <t>-1,17</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-8,2%</t>
+          <t>-1,69%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-31,86; -0,19</t>
+          <t>-31,49; -0,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 18,05</t>
+          <t>-11,32; 18,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 26,34</t>
+          <t>-6,43; 25,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-26,83; 13,43</t>
+          <t>-15,54; 14,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-45,74; -0,86</t>
+          <t>-45,46; -1,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-22,33; 52,27</t>
+          <t>-24,01; 55,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-17,27; 91,18</t>
+          <t>-15,72; 84,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-36,63; 21,78</t>
+          <t>-21,02; 24,55</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,09</t>
+          <t>1,09</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 3,14</t>
+          <t>-9,06; 2,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 4,17</t>
+          <t>-7,72; 5,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 4,38</t>
+          <t>-6,78; 4,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 11,93</t>
+          <t>-3,9; 7,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-21,82; 10,12</t>
+          <t>-24,11; 7,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-20,34; 12,84</t>
+          <t>-20,15; 15,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-19,97; 14,27</t>
+          <t>-18,75; 13,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 16,82</t>
+          <t>-4,81; 10,36</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,71</t>
+          <t>-0,68</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-0,91%</t>
+          <t>-0,87%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,24; 5,7</t>
+          <t>-12,31; 6,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 12,86</t>
+          <t>-5,93; 13,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 13,69</t>
+          <t>-4,75; 13,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 7,52</t>
+          <t>-8,41; 8,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-35,3; 20,62</t>
+          <t>-33,5; 25,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,2; 50,01</t>
+          <t>-16,51; 50,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-16,51; 51,27</t>
+          <t>-13,68; 48,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,25; 10,35</t>
+          <t>-10,38; 11,59</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,17</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 0,45</t>
+          <t>-9,27; 0,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 5,31</t>
+          <t>-4,78; 5,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 5,72</t>
+          <t>-4,09; 5,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 7,86</t>
+          <t>-3,65; 5,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-22,7; 1,33</t>
+          <t>-23,54; 1,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,64; 16,28</t>
+          <t>-12,67; 15,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,79; 18,44</t>
+          <t>-11,5; 16,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 10,91</t>
+          <t>-4,64; 6,75</t>
         </is>
       </c>
     </row>
